--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487438_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487438_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3288</v>
+        <v>9.756600000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.445</v>
+        <v>7.1936</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8838</v>
+        <v>2.563</v>
       </c>
       <c r="G2" t="n">
         <v>6.4195</v>
@@ -610,13 +610,13 @@
         <v>1.7626</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7353</v>
+        <v>2.1632</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6776</v>
+        <v>1.4262</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0577</v>
+        <v>0.7369</v>
       </c>
       <c r="V2" t="n">
         <v>0.3905</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.1182</v>
+        <v>9.7232</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7192</v>
+        <v>7.2707</v>
       </c>
       <c r="F3" t="n">
-        <v>2.399</v>
+        <v>2.4525</v>
       </c>
       <c r="G3" t="n">
         <v>4.3072</v>
@@ -688,13 +688,13 @@
         <v>2.7419</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3641</v>
+        <v>0.2408</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1286</v>
+        <v>0.4229</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2355</v>
+        <v>-0.182</v>
       </c>
       <c r="V3" t="n">
         <v>2.4332</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.0589</v>
+        <v>8.792899999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1056</v>
+        <v>5.7594</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9533</v>
+        <v>3.0335</v>
       </c>
       <c r="G4" t="n">
         <v>6.8753</v>
@@ -766,13 +766,13 @@
         <v>2.9377</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3463</v>
+        <v>0.3877</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1286</v>
+        <v>0.5252</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2177</v>
+        <v>-0.1375</v>
       </c>
       <c r="V4" t="n">
         <v>0.5507</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.9529</v>
+        <v>4.2392</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3273</v>
+        <v>4.9345</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3744</v>
+        <v>-0.6952</v>
       </c>
       <c r="G5" t="n">
         <v>4.2978</v>
@@ -844,13 +844,13 @@
         <v>0.5875</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3418</v>
+        <v>0.6281</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8299</v>
+        <v>0.437</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5119</v>
+        <v>0.1911</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2742</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>D. LEMOINE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3473</v>
+        <v>3.0685</v>
       </c>
       <c r="E6" t="n">
-        <v>1.771</v>
+        <v>3.7027</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5763</v>
+        <v>-0.6341</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9573</v>
+        <v>2.1407</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6393</v>
+        <v>0.8874</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5966</v>
+        <v>1.2532</v>
       </c>
       <c r="J6" t="n">
-        <v>1.951</v>
+        <v>2.3251</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0342</v>
+        <v>0.951</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9852</v>
+        <v>1.3741</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9938</v>
+        <v>-0.1844</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6052</v>
+        <v>-0.0635</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3886</v>
+        <v>-0.1209</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1958</v>
+        <v>1.7626</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1543</v>
+        <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8037</v>
+        <v>0.9901</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7785</v>
+        <v>0.7693</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0252</v>
+        <v>0.2209</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3905</v>
+        <v>-1.8249</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3905</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ROA RODRIGUEZ</t>
+          <t>A. CASADO MANCERAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6535</v>
+        <v>3.0422</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3494</v>
+        <v>0.8666</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3041</v>
+        <v>2.1757</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1471</v>
+        <v>3.165</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2331</v>
+        <v>2.3315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.8335</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9043</v>
+        <v>2.1328</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9851</v>
+        <v>2.1232</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0808</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7572</v>
+        <v>1.0322</v>
       </c>
       <c r="N7" t="n">
-        <v>0.752</v>
+        <v>0.2083</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0052</v>
+        <v>0.8239</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9964</v>
+        <v>0.2689</v>
       </c>
       <c r="T7" t="n">
-        <v>3.233</v>
+        <v>0.6922</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2365</v>
+        <v>-0.4233</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CASADO MANCERAS</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5481</v>
+        <v>2.7055</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5595</v>
+        <v>0.9688</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9886</v>
+        <v>1.7367</v>
       </c>
       <c r="G8" t="n">
-        <v>3.165</v>
+        <v>0.9573</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3315</v>
+        <v>-0.6393</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8335</v>
+        <v>1.5966</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1328</v>
+        <v>1.951</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1232</v>
+        <v>-0.0342</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009599999999999999</v>
+        <v>1.9852</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0322</v>
+        <v>-0.9938</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2083</v>
+        <v>-0.6052</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8239</v>
+        <v>-0.3886</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5668</v>
+        <v>2.1543</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2252</v>
+        <v>1.1619</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3852</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6104000000000001</v>
+        <v>0.1856</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3905</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. LEMOINE</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1032</v>
+        <v>2.6038</v>
       </c>
       <c r="E9" t="n">
-        <v>2.577</v>
+        <v>2.8144</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4737</v>
+        <v>-0.2106</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1407</v>
+        <v>3.1181</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8874</v>
+        <v>2.6175</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2532</v>
+        <v>0.5006</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3251</v>
+        <v>3.3743</v>
       </c>
       <c r="K9" t="n">
-        <v>0.951</v>
+        <v>3.2935</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3741</v>
+        <v>0.0808</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1844</v>
+        <v>-0.2563</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0635</v>
+        <v>-0.676</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1209</v>
+        <v>0.4197</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7626</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7626</v>
+        <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0248</v>
+        <v>0.7024</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3564</v>
+        <v>0.4193</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3812</v>
+        <v>0.283</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8249</v>
+        <v>-1.2166</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4332</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>R. SANCHEZ PARRES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5816</v>
+        <v>0.5897</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9793</v>
+        <v>0.1939</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3977</v>
+        <v>0.3958</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1181</v>
+        <v>0.8068</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6175</v>
+        <v>1.3978</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5006</v>
+        <v>-0.591</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3743</v>
+        <v>0.5214</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2935</v>
+        <v>1.1228</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0808</v>
+        <v>-0.6014</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2563</v>
+        <v>0.2854</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.676</v>
+        <v>0.275</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4197</v>
+        <v>0.0104</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9792</v>
+        <v>0.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3199</v>
+        <v>0.0951</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4158</v>
+        <v>0.3764</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0959</v>
+        <v>-0.2813</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. SANCHEZ PARRES</t>
+          <t>A. ROA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2649</v>
+        <v>0.4999</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4201</v>
+        <v>-0.6973</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1552</v>
+        <v>1.1971</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8068</v>
+        <v>-0.1471</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3978</v>
+        <v>-0.2331</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.591</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5214</v>
+        <v>-0.9043</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1228</v>
+        <v>-0.9851</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6014</v>
+        <v>0.0808</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2854</v>
+        <v>0.7572</v>
       </c>
       <c r="N11" t="n">
-        <v>0.275</v>
+        <v>0.752</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0104</v>
+        <v>0.0052</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5875</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7595</v>
+        <v>0.8428</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2376</v>
+        <v>1.1863</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5219</v>
+        <v>-0.3435</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>44.42760000000001</v>
+        <v>45.0215</v>
       </c>
       <c r="E12" t="n">
-        <v>32.4132</v>
+        <v>33.0073</v>
       </c>
       <c r="F12" t="n">
-        <v>12.0145</v>
+        <v>12.0144</v>
       </c>
       <c r="G12" t="n">
         <v>31.9406</v>
@@ -1375,7 +1375,7 @@
         <v>0.1817</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6302</v>
+        <v>-0.6302000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0.8119999999999999</v>
@@ -1390,10 +1390,10 @@
         <v>15.6677</v>
       </c>
       <c r="S12" t="n">
-        <v>6.887</v>
+        <v>7.481</v>
       </c>
       <c r="T12" t="n">
-        <v>6.6372</v>
+        <v>7.231100000000001</v>
       </c>
       <c r="U12" t="n">
         <v>0.2498999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0796</v>
+        <v>-0.1472</v>
       </c>
       <c r="E13" t="n">
-        <v>2.428</v>
+        <v>2.121</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3484</v>
+        <v>-2.2682</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2789</v>
@@ -1468,13 +1468,13 @@
         <v>0.9792</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3793</v>
+        <v>0.1525</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0081</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6288</v>
+        <v>-0.5486</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>H. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9257</v>
+        <v>-1.3269</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4409</v>
+        <v>-0.8955</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3666</v>
+        <v>-0.4315</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7631</v>
+        <v>-0.2987</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5406</v>
+        <v>-0.2987</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2225</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>4.0191</v>
+        <v>0.0408</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9382</v>
+        <v>0.0408</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0808</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.256</v>
+        <v>-0.3396</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.3977</v>
+        <v>-0.3396</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1416</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1903</v>
+        <v>-0.049</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1911</v>
+        <v>0.0429</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3814</v>
+        <v>-0.0919</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. FERNANDEZ GONZALEZ</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.456</v>
+        <v>-1.429</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9978</v>
+        <v>1.3386</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4582</v>
+        <v>-2.7675</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2987</v>
+        <v>0.7631</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2987</v>
+        <v>0.5406</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.2225</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0408</v>
+        <v>4.0191</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0408</v>
+        <v>3.9382</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.0808</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3396</v>
+        <v>-3.256</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3396</v>
+        <v>-3.3977</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.1416</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.178</v>
+        <v>-0.313</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0594</v>
+        <v>-0.2935</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1186</v>
+        <v>-0.0196</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. GUERRA TRUJILLO</t>
+          <t>G. PREOTU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.9386</v>
+        <v>-2.995</v>
       </c>
       <c r="E16" t="n">
-        <v>1.825</v>
+        <v>-1.7077</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.7636</v>
+        <v>-1.2872</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.2097</v>
+        <v>-2.3217</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.4111</v>
+        <v>-0.331</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.7987</v>
+        <v>-1.9907</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.237</v>
+        <v>-0.6385</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7164</v>
+        <v>0.6856</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5206</v>
+        <v>-1.3241</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.9727</v>
+        <v>-1.6833</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6947</v>
+        <v>-1.0166</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2781</v>
+        <v>-0.6667</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3709</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6248</v>
+        <v>-0.6145</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7866</v>
+        <v>-0.09</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1618</v>
+        <v>-0.5245</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2754</v>
+        <v>0.3329</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PREOTU</t>
+          <t>X. RUBIN CARBALLEIRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.1821</v>
+        <v>-3.3412</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7077</v>
+        <v>-1.8813</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4743</v>
+        <v>-1.4599</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3217</v>
+        <v>-0.8183</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.331</v>
+        <v>-0.591</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9907</v>
+        <v>-0.2273</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6385</v>
+        <v>0.0608</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6856</v>
+        <v>0.0204</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3241</v>
+        <v>0.0404</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6833</v>
+        <v>-0.8791</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0166</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6667</v>
+        <v>-0.2677</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8016</v>
+        <v>-0.7982</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.09</v>
+        <v>-0.297</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7116</v>
+        <v>-0.5012</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3329</v>
+        <v>-0.9412</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3329</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. RUBIN CARBALLEIRA</t>
+          <t>D. GUERRA TRUJILLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.3679</v>
+        <v>-3.6249</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8813</v>
+        <v>0.0853</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4866</v>
+        <v>-3.7101</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8183</v>
+        <v>-5.2097</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.591</v>
+        <v>-2.4111</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2273</v>
+        <v>-2.7987</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0608</v>
+        <v>-1.237</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0204</v>
+        <v>-0.7164</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0404</v>
+        <v>-0.5206</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8791</v>
+        <v>-3.9727</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-1.6947</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2677</v>
+        <v>-2.2781</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1958</v>
+        <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.825</v>
+        <v>-0.0615</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.297</v>
+        <v>1.0469</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.528</v>
+        <v>-1.1083</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9412</v>
+        <v>0.2754</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.4473</v>
+        <v>-4.3671</v>
       </c>
       <c r="E19" t="n">
         <v>-2.9363</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.511</v>
+        <v>-1.4308</v>
       </c>
       <c r="G19" t="n">
         <v>-1.9724</v>
@@ -1936,13 +1936,13 @@
         <v>0.1958</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7123</v>
+        <v>-0.6321</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3564</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3559</v>
+        <v>-0.2757</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.0534</v>
+        <v>-5.0267</v>
       </c>
       <c r="E20" t="n">
         <v>-1.948</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1054</v>
+        <v>-3.0787</v>
       </c>
       <c r="G20" t="n">
         <v>-4.6552</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0481</v>
+        <v>-0.0213</v>
       </c>
       <c r="T20" t="n">
         <v>0.3723</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4203</v>
+        <v>-0.3936</v>
       </c>
       <c r="V20" t="n">
         <v>1.2166</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6806</v>
+        <v>-5.7562</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9816</v>
+        <v>-3.084</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6989</v>
+        <v>-2.6722</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0911</v>
@@ -2092,13 +2092,13 @@
         <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8844</v>
+        <v>-0.96</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2506</v>
+        <v>-0.3529</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6338</v>
+        <v>-0.6071</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5507</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. LOPEZ MOURE</t>
+          <t>A. HARRIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.0817</v>
+        <v>-8.039099999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7601</v>
+        <v>-0.2673</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.3216</v>
+        <v>-7.7718</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.7881</v>
+        <v>-7.2693</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.4385</v>
+        <v>-7.7079</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3496</v>
+        <v>0.4386</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3134</v>
+        <v>-0.303</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1106</v>
+        <v>-3.1562</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2028</v>
+        <v>2.8532</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.4747</v>
+        <v>-6.9663</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.3279</v>
+        <v>-4.5517</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.1468</v>
+        <v>-2.4145</v>
       </c>
       <c r="P22" t="n">
         <v>0.7834</v>
@@ -2170,28 +2170,28 @@
         <v>1.7626</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.4686</v>
+        <v>-1.8285</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4674</v>
+        <v>-0.477</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0012</v>
+        <v>-1.3515</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. HARRIS</t>
+          <t>D. LOPEZ MOURE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.374000000000001</v>
+        <v>-8.374499999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4953</v>
+        <v>-2.8391</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.8787</v>
+        <v>-5.5354</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.2693</v>
+        <v>-6.7881</v>
       </c>
       <c r="H23" t="n">
-        <v>-7.7079</v>
+        <v>-3.4385</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4386</v>
+        <v>-3.3496</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.303</v>
+        <v>-1.3134</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.1562</v>
+        <v>-0.1106</v>
       </c>
       <c r="L23" t="n">
-        <v>2.8532</v>
+        <v>-1.2028</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.9663</v>
+        <v>-5.4747</v>
       </c>
       <c r="N23" t="n">
-        <v>-4.5517</v>
+        <v>-3.3279</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.4145</v>
+        <v>-2.1468</v>
       </c>
       <c r="P23" t="n">
         <v>0.7834</v>
@@ -2248,22 +2248,22 @@
         <v>1.7626</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.1635</v>
+        <v>-1.7615</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.705</v>
+        <v>-0.5464</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4585</v>
+        <v>-1.2151</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2754</v>
+        <v>-0.6083</v>
       </c>
       <c r="W23" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="24">
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-44.4277</v>
+        <v>-44.4278</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.0142</v>
+        <v>-12.0143</v>
       </c>
       <c r="F24" t="n">
         <v>-32.4133</v>
@@ -2299,13 +2299,13 @@
         <v>-11.5201</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1818000000000002</v>
+        <v>-0.1817999999999997</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6301999999999999</v>
+        <v>0.6302000000000005</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8121</v>
+        <v>-0.8120999999999998</v>
       </c>
       <c r="M24" t="n">
         <v>-31.7587</v>
@@ -2329,7 +2329,7 @@
         <v>-6.8871</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2499000000000002</v>
+        <v>-0.2499999999999999</v>
       </c>
       <c r="U24" t="n">
         <v>-6.6371</v>
